--- a/Excel/Book1.xlsx
+++ b/Excel/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FBS\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CEC9E5B-9A0B-40C1-AA59-CD59C66CF486}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05588E59-EC56-45F0-BB6C-1CE6EC862759}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7480" windowHeight="1650" xr2:uid="{212CA19A-E2C6-4D31-9A02-E32EE89465A5}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="61">
   <si>
     <t>prasad</t>
   </si>
@@ -151,13 +151,70 @@
   </si>
   <si>
     <t>Dates</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Course</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Panvel</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>Koparkhairane</t>
+  </si>
+  <si>
+    <t>Java</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Csmt</t>
+  </si>
+  <si>
+    <t>New Panvel</t>
+  </si>
+  <si>
+    <t>Data analyst</t>
+  </si>
+  <si>
+    <t>Kharghar</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Sujata</t>
+  </si>
+  <si>
+    <t>Diva</t>
+  </si>
+  <si>
+    <t>Bhiwandi</t>
+  </si>
+  <si>
+    <t>Cyber</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,8 +229,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -210,6 +275,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -238,7 +309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -265,6 +336,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -580,10 +657,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA54C73-A1ED-4F34-BC77-4167A9220BDC}">
-  <dimension ref="D4:P67"/>
+  <dimension ref="B4:P88"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="11.36328125" customWidth="1"/>
+    <col min="5" max="5" width="13.6328125" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" customWidth="1"/>
     <col min="7" max="7" width="18.26953125" customWidth="1"/>
     <col min="8" max="8" width="18.453125" customWidth="1"/>
     <col min="9" max="9" width="30.26953125" customWidth="1"/>
@@ -1127,7 +1206,7 @@
         <v>2014</v>
       </c>
       <c r="I45" s="3">
-        <f t="shared" ref="I45:I47" si="7">DATE(H45,G45,F45)</f>
+        <f t="shared" ref="I45:I46" si="7">DATE(H45,G45,F45)</f>
         <v>41680</v>
       </c>
       <c r="L45" s="12">
@@ -1284,11 +1363,11 @@
       </c>
       <c r="H58" s="8">
         <f ca="1">NOW()</f>
-        <v>46195.703091435185</v>
+        <v>46200.001505787041</v>
       </c>
       <c r="I58" s="8">
         <f ca="1">NOW() + 1</f>
-        <v>46196.703091435185</v>
+        <v>46201.001505787041</v>
       </c>
     </row>
     <row r="59" spans="4:9" x14ac:dyDescent="0.35">
@@ -1307,18 +1386,18 @@
       </c>
       <c r="H59" s="8">
         <f ca="1">NOW()</f>
-        <v>46195.703091435185</v>
+        <v>46200.001505787041</v>
       </c>
       <c r="I59">
         <f ca="1">NOW() + 2 / 24</f>
-        <v>46195.786424768521</v>
+        <v>46200.084839120376</v>
       </c>
     </row>
     <row r="60" spans="4:9" x14ac:dyDescent="0.35">
       <c r="G60" s="10"/>
       <c r="H60" s="8">
         <f ca="1">NOW()</f>
-        <v>46195.703091435185</v>
+        <v>46200.001505787041</v>
       </c>
     </row>
     <row r="62" spans="4:9" x14ac:dyDescent="0.35">
@@ -1338,20 +1417,226 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="65" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="D65" s="3" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="66" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="D66" s="3" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="67" spans="4:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.35">
       <c r="D67" s="3"/>
+    </row>
+    <row r="70" spans="2:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B70" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E70" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F70" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B71" s="15">
+        <v>101</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E71" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F71" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B72" s="15">
+        <v>102</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F72" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B73" s="15">
+        <v>103</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B74" s="15">
+        <v>104</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E74" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F74" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B75" s="15">
+        <v>105</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E75" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F75" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B76" s="15">
+        <v>106</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E76" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F76" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B77" s="15">
+        <v>107</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E77" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F77" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C80" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E80" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F80" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B81">
+        <v>102</v>
+      </c>
+      <c r="C81" t="str">
+        <f>LOOKUP($B$81,$B$71:$B$77,C71:C77)</f>
+        <v>Nikhil</v>
+      </c>
+      <c r="D81" t="str">
+        <f t="shared" ref="D81:F81" si="13">LOOKUP($B$81,$B$71:$B$77,D71:D77)</f>
+        <v>Male</v>
+      </c>
+      <c r="E81" t="str">
+        <f t="shared" si="13"/>
+        <v>Koparkhairane</v>
+      </c>
+      <c r="F81" t="str">
+        <f t="shared" si="13"/>
+        <v>Java</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B82">
+        <v>103</v>
+      </c>
+      <c r="C82" t="str">
+        <f>LOOKUP($B$82,$B$71:$B$77,C71:C77)</f>
+        <v>Katta</v>
+      </c>
+      <c r="D82" t="str">
+        <f t="shared" ref="D82:F82" si="14">LOOKUP($B$82,$B$71:$B$77,D71:D77)</f>
+        <v>Female</v>
+      </c>
+      <c r="E82" t="str">
+        <f t="shared" si="14"/>
+        <v>Csmt</v>
+      </c>
+      <c r="F82" t="str">
+        <f t="shared" si="14"/>
+        <v>Java</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C88" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E88" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88" s="16" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/Book1.xlsx
+++ b/Excel/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FBS\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05588E59-EC56-45F0-BB6C-1CE6EC862759}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3203BA1D-99DD-4287-85C7-080F0F48AC99}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7480" windowHeight="1650" xr2:uid="{212CA19A-E2C6-4D31-9A02-E32EE89465A5}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="74">
   <si>
     <t>prasad</t>
   </si>
@@ -208,13 +208,52 @@
   </si>
   <si>
     <t>Cyber</t>
+  </si>
+  <si>
+    <t>LOOKUP</t>
+  </si>
+  <si>
+    <t>VLOOKUP</t>
+  </si>
+  <si>
+    <t>MATCH</t>
+  </si>
+  <si>
+    <t>Matches gives index number</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Vishal</t>
+  </si>
+  <si>
+    <t>Uran</t>
+  </si>
+  <si>
+    <t>Thane</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,6 +272,14 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -309,7 +356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -341,6 +388,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -657,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA54C73-A1ED-4F34-BC77-4167A9220BDC}">
-  <dimension ref="B4:P88"/>
+  <dimension ref="B4:P110"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="11.36328125" customWidth="1"/>
@@ -1363,11 +1417,11 @@
       </c>
       <c r="H58" s="8">
         <f ca="1">NOW()</f>
-        <v>46200.001505787041</v>
+        <v>46205.982344560187</v>
       </c>
       <c r="I58" s="8">
         <f ca="1">NOW() + 1</f>
-        <v>46201.001505787041</v>
+        <v>46206.982344560187</v>
       </c>
     </row>
     <row r="59" spans="4:9" x14ac:dyDescent="0.35">
@@ -1386,18 +1440,18 @@
       </c>
       <c r="H59" s="8">
         <f ca="1">NOW()</f>
-        <v>46200.001505787041</v>
+        <v>46205.982344560187</v>
       </c>
       <c r="I59">
         <f ca="1">NOW() + 2 / 24</f>
-        <v>46200.084839120376</v>
+        <v>46206.065677893523</v>
       </c>
     </row>
     <row r="60" spans="4:9" x14ac:dyDescent="0.35">
       <c r="G60" s="10"/>
       <c r="H60" s="8">
         <f ca="1">NOW()</f>
-        <v>46200.001505787041</v>
+        <v>46205.982344560187</v>
       </c>
     </row>
     <row r="62" spans="4:9" x14ac:dyDescent="0.35">
@@ -1417,22 +1471,22 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.35">
       <c r="D65" s="3" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.35">
       <c r="D66" s="3" t="e">
         <f t="shared" si="12"/>
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.35">
       <c r="D67" s="3"/>
     </row>
-    <row r="70" spans="2:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B70" s="16" t="s">
         <v>42</v>
       </c>
@@ -1449,7 +1503,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B71" s="15">
         <v>101</v>
       </c>
@@ -1466,7 +1520,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B72" s="15">
         <v>102</v>
       </c>
@@ -1483,7 +1537,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B73" s="15">
         <v>103</v>
       </c>
@@ -1500,7 +1554,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B74" s="15">
         <v>104</v>
       </c>
@@ -1517,7 +1571,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B75" s="15">
         <v>105</v>
       </c>
@@ -1534,7 +1588,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B76" s="15">
         <v>106</v>
       </c>
@@ -1551,7 +1605,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B77" s="15">
         <v>107</v>
       </c>
@@ -1568,7 +1622,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="80" spans="2:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C80" s="16" t="s">
         <v>12</v>
       </c>
@@ -1581,8 +1635,11 @@
       <c r="F80" s="16" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="G80" s="17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B81">
         <v>102</v>
       </c>
@@ -1603,16 +1660,16 @@
         <v>Java</v>
       </c>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B82">
         <v>103</v>
       </c>
       <c r="C82" t="str">
-        <f>LOOKUP($B$82,$B$71:$B$77,C71:C77)</f>
+        <f t="shared" ref="C82:F84" si="14">LOOKUP($B$81,$B$71:$B$77,C72:C78)</f>
         <v>Katta</v>
       </c>
       <c r="D82" t="str">
-        <f t="shared" ref="D82:F82" si="14">LOOKUP($B$82,$B$71:$B$77,D71:D77)</f>
+        <f t="shared" si="14"/>
         <v>Female</v>
       </c>
       <c r="E82" t="str">
@@ -1624,7 +1681,49 @@
         <v>Java</v>
       </c>
     </row>
-    <row r="88" spans="2:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B83">
+        <v>104</v>
+      </c>
+      <c r="C83" t="str">
+        <f t="shared" si="14"/>
+        <v>Durvesh</v>
+      </c>
+      <c r="D83" t="str">
+        <f t="shared" si="14"/>
+        <v>Male</v>
+      </c>
+      <c r="E83" t="str">
+        <f t="shared" si="14"/>
+        <v>New Panvel</v>
+      </c>
+      <c r="F83" t="str">
+        <f t="shared" si="14"/>
+        <v>Data analyst</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B84">
+        <v>105</v>
+      </c>
+      <c r="C84" t="str">
+        <f t="shared" si="14"/>
+        <v>Gauri</v>
+      </c>
+      <c r="D84" t="str">
+        <f t="shared" si="14"/>
+        <v>Female</v>
+      </c>
+      <c r="E84" t="str">
+        <f t="shared" si="14"/>
+        <v>Kharghar</v>
+      </c>
+      <c r="F84" t="str">
+        <f t="shared" si="14"/>
+        <v>Testing</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C88" s="16" t="s">
         <v>12</v>
       </c>
@@ -1634,11 +1733,216 @@
       <c r="E88" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="F88" s="16" t="s">
-        <v>45</v>
-      </c>
+      <c r="F88" s="16"/>
+      <c r="G88" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B89">
+        <v>105</v>
+      </c>
+      <c r="C89" t="str">
+        <f>VLOOKUP($B$89,$B$70:$F$77,MATCH(C88,$B$70:$F$70,0),FALSE)</f>
+        <v>Gauri</v>
+      </c>
+      <c r="D89" t="str">
+        <f>VLOOKUP($B$89,$B$70:$F$77,MATCH(D88,$B$70:$F$70,0),FALSE)</f>
+        <v>Female</v>
+      </c>
+      <c r="E89" t="str">
+        <f t="shared" ref="E89:F89" si="15">VLOOKUP($B$89,$B$70:$F$77,MATCH(E88,$B$70:$F$70,0),FALSE)</f>
+        <v>Kharghar</v>
+      </c>
+      <c r="F89" t="e">
+        <f t="shared" si="15"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="D92" t="s">
+        <v>57</v>
+      </c>
+      <c r="E92" s="5">
+        <f>MATCH(D92,C70:C77,0)</f>
+        <v>7</v>
+      </c>
+      <c r="F92" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G92" s="18" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="99" spans="3:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C99" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D99" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E99" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F99" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="100" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C100" s="15">
+        <v>101</v>
+      </c>
+      <c r="D100" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E100" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F100" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="101" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C101" s="15">
+        <v>102</v>
+      </c>
+      <c r="D101" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F101" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="102" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C102" s="15">
+        <v>103</v>
+      </c>
+      <c r="D102" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E102" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F102" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="103" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C103" s="15">
+        <v>104</v>
+      </c>
+      <c r="D103" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E103" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F103" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="104" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C104" s="15">
+        <v>105</v>
+      </c>
+      <c r="D104" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E104" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F104" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="105" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C105" s="15">
+        <v>106</v>
+      </c>
+      <c r="D105" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E105" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F105" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="106" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C106" s="15">
+        <v>107</v>
+      </c>
+      <c r="D106" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E106" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F106" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="107" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C107" s="15">
+        <v>108</v>
+      </c>
+      <c r="D107" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E107" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F107" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="108" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C108" s="15">
+        <v>109</v>
+      </c>
+      <c r="D108" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E108" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F108" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="109" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C109" s="15">
+        <v>110</v>
+      </c>
+      <c r="D109" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E109" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F109" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="110" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="C110" s="19"/>
+      <c r="D110" s="19"/>
+      <c r="E110" s="19"/>
+      <c r="F110" s="19"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D92" xr:uid="{6D90D5A9-A5C4-4DC3-9945-0ABB6AD4134F}">
+      <formula1>$C$71:$C$77</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B89" xr:uid="{73A56180-B2E8-4FD0-9E96-9A2D7DB1C51F}">
+      <formula1>$B$71:$B$77</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Excel/Book1.xlsx
+++ b/Excel/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FBS\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3203BA1D-99DD-4287-85C7-080F0F48AC99}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448DE34A-7ED1-4205-A703-52006BFA1AED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7480" windowHeight="1650" xr2:uid="{212CA19A-E2C6-4D31-9A02-E32EE89465A5}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="2" r:id="rId2"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="78">
   <si>
     <t>prasad</t>
   </si>
@@ -247,6 +250,18 @@
   </si>
   <si>
     <t>Thane</t>
+  </si>
+  <si>
+    <t>IFERROR</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Count of Name</t>
   </si>
 </sst>
 </file>
@@ -356,7 +371,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -397,6 +412,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,6 +432,163 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Admin" refreshedDate="46207.974120833336" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="10" xr:uid="{F8454E76-4E76-4CBC-8829-0782E1A2027A}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="C99:F109" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="4">
+    <cacheField name="ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="101" maxValue="110"/>
+    </cacheField>
+    <cacheField name="Name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Department" numFmtId="0">
+      <sharedItems count="5">
+        <s v="IT"/>
+        <s v="Admin"/>
+        <s v="HR"/>
+        <s v="Sales"/>
+        <s v="Finance"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="City" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="10">
+  <r>
+    <n v="101"/>
+    <s v="Prasad"/>
+    <x v="0"/>
+    <s v="Panvel"/>
+  </r>
+  <r>
+    <n v="102"/>
+    <s v="Nikhil"/>
+    <x v="1"/>
+    <s v="Koparkhairane"/>
+  </r>
+  <r>
+    <n v="103"/>
+    <s v="Katta"/>
+    <x v="2"/>
+    <s v="Csmt"/>
+  </r>
+  <r>
+    <n v="104"/>
+    <s v="Durvesh"/>
+    <x v="3"/>
+    <s v="New Panvel"/>
+  </r>
+  <r>
+    <n v="105"/>
+    <s v="Gauri"/>
+    <x v="4"/>
+    <s v="Kharghar"/>
+  </r>
+  <r>
+    <n v="106"/>
+    <s v="Sujata"/>
+    <x v="0"/>
+    <s v="Diva"/>
+  </r>
+  <r>
+    <n v="107"/>
+    <s v="Pranav"/>
+    <x v="3"/>
+    <s v="Bhiwandi"/>
+  </r>
+  <r>
+    <n v="108"/>
+    <s v="Vishal"/>
+    <x v="1"/>
+    <s v="Uran"/>
+  </r>
+  <r>
+    <n v="109"/>
+    <s v="Vedant"/>
+    <x v="4"/>
+    <s v="Thane"/>
+  </r>
+  <r>
+    <n v="110"/>
+    <s v="Prathamesh"/>
+    <x v="2"/>
+    <s v="Thane"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CBF27097-895F-4EB4-9231-6367E31D295E}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="H106:I112" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -711,15 +888,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA54C73-A1ED-4F34-BC77-4167A9220BDC}">
-  <dimension ref="B4:P110"/>
+  <dimension ref="B4:P120"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="11.36328125" customWidth="1"/>
     <col min="5" max="5" width="13.6328125" customWidth="1"/>
     <col min="6" max="6" width="12.26953125" customWidth="1"/>
     <col min="7" max="7" width="18.26953125" customWidth="1"/>
-    <col min="8" max="8" width="18.453125" customWidth="1"/>
-    <col min="9" max="9" width="30.26953125" customWidth="1"/>
+    <col min="8" max="8" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.90625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.26953125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1417,11 +1595,11 @@
       </c>
       <c r="H58" s="8">
         <f ca="1">NOW()</f>
-        <v>46205.982344560187</v>
+        <v>46208.02595289352</v>
       </c>
       <c r="I58" s="8">
         <f ca="1">NOW() + 1</f>
-        <v>46206.982344560187</v>
+        <v>46209.02595289352</v>
       </c>
     </row>
     <row r="59" spans="4:9" x14ac:dyDescent="0.35">
@@ -1440,18 +1618,18 @@
       </c>
       <c r="H59" s="8">
         <f ca="1">NOW()</f>
-        <v>46205.982344560187</v>
+        <v>46208.02595289352</v>
       </c>
       <c r="I59">
         <f ca="1">NOW() + 2 / 24</f>
-        <v>46206.065677893523</v>
+        <v>46208.109286226856</v>
       </c>
     </row>
     <row r="60" spans="4:9" x14ac:dyDescent="0.35">
       <c r="G60" s="10"/>
       <c r="H60" s="8">
         <f ca="1">NOW()</f>
-        <v>46205.982344560187</v>
+        <v>46208.02595289352</v>
       </c>
     </row>
     <row r="62" spans="4:9" x14ac:dyDescent="0.35">
@@ -1774,7 +1952,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="3:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C99" s="16" t="s">
         <v>42</v>
       </c>
@@ -1788,7 +1966,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="100" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C100" s="15">
         <v>101</v>
       </c>
@@ -1802,7 +1980,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="101" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C101" s="15">
         <v>102</v>
       </c>
@@ -1816,7 +1994,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="102" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C102" s="15">
         <v>103</v>
       </c>
@@ -1830,7 +2008,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="103" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C103" s="15">
         <v>104</v>
       </c>
@@ -1844,7 +2022,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="104" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C104" s="15">
         <v>105</v>
       </c>
@@ -1858,7 +2036,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="105" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C105" s="15">
         <v>106</v>
       </c>
@@ -1872,7 +2050,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="106" spans="3:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C106" s="15">
         <v>107</v>
       </c>
@@ -1885,8 +2063,14 @@
       <c r="F106" s="15" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="107" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="H106" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I106" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="107" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C107" s="15">
         <v>108</v>
       </c>
@@ -1899,8 +2083,14 @@
       <c r="F107" s="15" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="108" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="H107" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="I107" s="22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C108" s="15">
         <v>109</v>
       </c>
@@ -1913,8 +2103,14 @@
       <c r="F108" s="15" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="109" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="H108" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I108" s="22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C109" s="15">
         <v>110</v>
       </c>
@@ -1927,23 +2123,115 @@
       <c r="F109" s="15" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="110" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="H109" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I109" s="22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C110" s="19"/>
       <c r="D110" s="19"/>
       <c r="E110" s="19"/>
       <c r="F110" s="19"/>
+      <c r="H110" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="I110" s="22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="H111" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I111" s="22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="3:9" x14ac:dyDescent="0.35">
+      <c r="H112" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="I112" s="22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="4:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="D113" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E113" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F113" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G113" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="114" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D114" s="4">
+        <v>102</v>
+      </c>
+      <c r="E114" s="4" t="str">
+        <f>IFERROR(INDEX($C$100:$F$109,
+MATCH($D$114,$C$100:$C$109,0),
+MATCH(E113,$C$99:$F$99,0)),"Wrong Input")</f>
+        <v>Nikhil</v>
+      </c>
+      <c r="F114" s="4" t="str">
+        <f>IFERROR(INDEX($C$100:$F$109,
+MATCH($D$114,$C$100:$C$109,0),
+MATCH(F113,$C$99:$F$99,0)),"Wrong Input")</f>
+        <v>Admin</v>
+      </c>
+    </row>
+    <row r="115" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D115" s="4"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4"/>
+    </row>
+    <row r="116" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D116" s="4"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+    </row>
+    <row r="117" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
+    </row>
+    <row r="118" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D118" s="4"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4"/>
+    </row>
+    <row r="119" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+    </row>
+    <row r="120" spans="4:7" x14ac:dyDescent="0.35">
+      <c r="D120" s="4"/>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D92" xr:uid="{6D90D5A9-A5C4-4DC3-9945-0ABB6AD4134F}">
       <formula1>$C$71:$C$77</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B89" xr:uid="{73A56180-B2E8-4FD0-9E96-9A2D7DB1C51F}">
       <formula1>$B$71:$B$77</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D114" xr:uid="{5D254330-E9BB-4EC1-AC72-2CCC2544E892}">
+      <formula1>$C$100:$C$109</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>